--- a/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">

--- a/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">

--- a/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">

--- a/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Oxford/Birds/abundance.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
